--- a/artfynd/A 5003-2026 artfynd.xlsx
+++ b/artfynd/A 5003-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851030</v>
       </c>
       <c r="B2" t="n">
-        <v>91940</v>
+        <v>91946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>133850779</v>
       </c>
       <c r="B3" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133850780</v>
       </c>
       <c r="B4" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5003-2026 artfynd.xlsx
+++ b/artfynd/A 5003-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851030</v>
       </c>
       <c r="B2" t="n">
-        <v>91946</v>
+        <v>91948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>133850779</v>
       </c>
       <c r="B3" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133850780</v>
       </c>
       <c r="B4" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5003-2026 artfynd.xlsx
+++ b/artfynd/A 5003-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851030</v>
       </c>
       <c r="B2" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>133850779</v>
       </c>
       <c r="B3" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133850780</v>
       </c>
       <c r="B4" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5003-2026 artfynd.xlsx
+++ b/artfynd/A 5003-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851030</v>
       </c>
       <c r="B2" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>133850779</v>
       </c>
       <c r="B3" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133850780</v>
       </c>
       <c r="B4" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5003-2026 artfynd.xlsx
+++ b/artfynd/A 5003-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851030</v>
       </c>
       <c r="B2" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>133850779</v>
       </c>
       <c r="B3" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133850780</v>
       </c>
       <c r="B4" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5003-2026 artfynd.xlsx
+++ b/artfynd/A 5003-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851030</v>
       </c>
       <c r="B2" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>133850779</v>
       </c>
       <c r="B3" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133850780</v>
       </c>
       <c r="B4" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5003-2026 artfynd.xlsx
+++ b/artfynd/A 5003-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133851030</v>
+        <v>133850779</v>
       </c>
       <c r="B2" t="n">
-        <v>91987</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622740</v>
+        <v>622751</v>
       </c>
       <c r="R2" t="n">
-        <v>7089312</v>
+        <v>7089342</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-44</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133850779</v>
+        <v>133850780</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622751</v>
+        <v>622668</v>
       </c>
       <c r="R3" t="n">
-        <v>7089342</v>
+        <v>7089299</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-50</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,108 +876,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>133850780</v>
-      </c>
-      <c r="B4" t="n">
-        <v>91967</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Skogen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>622668</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7089299</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-49</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5003-2026 artfynd.xlsx
+++ b/artfynd/A 5003-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850779</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850780</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>